--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_48.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6441843.979293765</v>
+        <v>6481781.158068844</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517476</v>
+        <v>2916902.906517466</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517476</v>
+        <v>2916902.906517466</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35914651.42422065</v>
+        <v>35914651.42422064</v>
       </c>
     </row>
   </sheetData>
@@ -657,10 +657,10 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>403.7573722870162</v>
+        <v>96.36700516145144</v>
       </c>
       <c r="H2" t="n">
         <v>8.009658703527407</v>
@@ -678,37 +678,37 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>748.0913712690565</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>297.9910820919849</v>
+        <v>814</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5855355810472</v>
+        <v>708.6062368062542</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>438.3363995050528</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -720,7 +720,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>241.2078457259398</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>300.0898026466166</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>114.969161706101</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>320.9396782847027</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>481.9993129555745</v>
+        <v>174.6089458300097</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -918,37 +918,37 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690067</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
-        <v>281.7754478641663</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>297.9910820919849</v>
+      </c>
+      <c r="N5" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O5" t="n">
+        <v>313.1545016101228</v>
+      </c>
+      <c r="P5" t="n">
         <v>814</v>
       </c>
-      <c r="N5" t="n">
-        <v>814</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>279.2852146029995</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -973,19 +973,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>189.3139912864827</v>
       </c>
       <c r="E6" t="n">
-        <v>148.6880250402009</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061042</v>
+        <v>91.42153354831777</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1137,61 +1137,61 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>96.3670051614515</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>418.7382696589336</v>
+        <v>634.7678887921559</v>
       </c>
       <c r="K8" t="n">
-        <v>507.7400371911694</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L8" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O8" t="n">
         <v>814</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>370.9706110579162</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>581.861707683677</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>57.72562438342283</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>167.1158402638075</v>
       </c>
     </row>
     <row r="10">
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617061073</v>
+        <v>114.9691617060916</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1371,10 +1371,10 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>179.8896287080119</v>
@@ -1413,13 +1413,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>60.43229665615095</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
         <v>424.2212965486107</v>
@@ -1431,10 +1431,10 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>50.65334830746249</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>342.1496093272373</v>
       </c>
       <c r="R13" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1605,13 +1605,13 @@
         <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>112.1646315222933</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
         <v>153.8896287080119</v>
@@ -1665,7 +1665,7 @@
         <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>387.3734759809475</v>
+        <v>147.7002396533783</v>
       </c>
       <c r="X14" t="n">
         <v>341.2818334606677</v>
@@ -1805,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G17" t="n">
         <v>124.7573722870162</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2030,22 +2030,22 @@
         <v>144.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>107.8765809499618</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>233.2453702959191</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>330.1216449083127</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>129.0096587035274</v>
+        <v>128.5790500890098</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>370.2212965486107</v>
       </c>
       <c r="V23" t="n">
-        <v>350.4204155522381</v>
+        <v>350.8510241668239</v>
       </c>
       <c r="W23" t="n">
         <v>359.3734759809475</v>
@@ -2501,28 +2501,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>49.23677672842039</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>233.2453702959191</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2553,16 +2553,16 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>58.19307777160522</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>378.3105735833417</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>367.2818334606677</v>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>342.1496093272373</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>85.49253616827886</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2796,16 +2796,16 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>36.59725481811878</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2847,7 +2847,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>286.3174326828064</v>
+        <v>276.5939301646475</v>
       </c>
     </row>
     <row r="30">
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>284.0117075345908</v>
       </c>
       <c r="N31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3051,31 +3051,31 @@
         <v>377.7382696589756</v>
       </c>
       <c r="K32" t="n">
-        <v>10.23281455304027</v>
+        <v>10.23281455293948</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>752.1594889580173</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>153.5855355810893</v>
       </c>
       <c r="O32" t="n">
         <v>773.0000000000421</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>170.9272644348425</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>757.6173000000409</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>203.8481678023229</v>
+        <v>212.3047591877378</v>
       </c>
       <c r="T32" t="n">
         <v>295.6755817285639</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>131.3113244366542</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>70.05053078764654</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>158.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>127.7957471252641</v>
+        <v>119.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>113.3632896068686</v>
@@ -3288,25 +3288,25 @@
         <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760183</v>
+        <v>56.12488247690044</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>656.4268144188952</v>
       </c>
       <c r="M35" t="n">
         <v>256.991082092034</v>
       </c>
       <c r="N35" t="n">
-        <v>551.2932893429992</v>
+        <v>153.5855355810966</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.970611057961</v>
+        <v>742.2346000000472</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="36">
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>108.4418998849671</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>226.7541306595264</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>190.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>166.9311696284081</v>
+        <v>158.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>119.3391557398498</v>
@@ -3522,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589902</v>
+        <v>757.6173000000554</v>
       </c>
       <c r="K38" t="n">
-        <v>397.7077537618591</v>
+        <v>712.6384842277645</v>
       </c>
       <c r="L38" t="n">
-        <v>727.107932076007</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>256.9910820920413</v>
@@ -3537,10 +3537,10 @@
         <v>153.5855355811038</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>32.29817126910682</v>
       </c>
       <c r="Q38" t="n">
         <v>329.9706110579683</v>
@@ -3567,7 +3567,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="39">
@@ -3686,28 +3686,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>81.22967444114592</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>387.1252532547462</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,22 +3786,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2.055070766100644</v>
       </c>
       <c r="W41" t="n">
         <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>277.0224030284859</v>
+        <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>298.3174326828064</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>334.2737972923793</v>
+        <v>50.78614729240174</v>
       </c>
       <c r="S42" t="n">
-        <v>116.0975572222915</v>
+        <v>253.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>210.5476281577792</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>76.56710727107678</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>247.0872575739518</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>180.0714614932957</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>462.2212965486107</v>
@@ -4038,7 +4038,7 @@
         <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>324.3174326828064</v>
@@ -4057,22 +4057,22 @@
         <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>28.29923008708757</v>
       </c>
       <c r="H45" t="n">
         <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>30.12638589134853</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,22 +4099,22 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>213.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>38.8435512689891</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>182.0259238883365</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510.488528253487</v>
+        <v>391.9123998438259</v>
       </c>
       <c r="C2" t="n">
-        <v>1056.473802755514</v>
+        <v>341.9380783862563</v>
       </c>
       <c r="D2" t="n">
-        <v>641.9898070586958</v>
+        <v>331.4944867298424</v>
       </c>
       <c r="E2" t="n">
-        <v>637.5824438194345</v>
+        <v>327.0871234905812</v>
       </c>
       <c r="F2" t="n">
-        <v>632.6434249224528</v>
+        <v>322.1481045935995</v>
       </c>
       <c r="G2" t="n">
         <v>224.8076953396081</v>
@@ -4321,22 +4321,22 @@
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>115.3321502332762</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L2" t="n">
-        <v>921.1921502332762</v>
+        <v>1961.626108953703</v>
       </c>
       <c r="M2" t="n">
-        <v>1426.051057211069</v>
+        <v>1945.263886731481</v>
       </c>
       <c r="N2" t="n">
-        <v>2035.360011169607</v>
+        <v>2035.360011169608</v>
       </c>
       <c r="O2" t="n">
-        <v>2841.220011169607</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2813.235960095906</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2624.67476643069</v>
+        <v>1910.139042061433</v>
       </c>
       <c r="U2" t="n">
-        <v>2372.936083048255</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V2" t="n">
-        <v>2140.763331364595</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W2" t="n">
-        <v>1899.982042494951</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X2" t="n">
-        <v>1705.757968292256</v>
+        <v>587.1818398825945</v>
       </c>
       <c r="Y2" t="n">
-        <v>1593.316117097502</v>
+        <v>474.7399886878406</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>528.0838703204934</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="C3" t="n">
-        <v>528.0838703204934</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="D3" t="n">
-        <v>528.0838703204934</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="E3" t="n">
-        <v>528.0838703204934</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="F3" t="n">
-        <v>284.4395817084329</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="G3" t="n">
-        <v>284.4395817084329</v>
+        <v>2403.688592405825</v>
       </c>
       <c r="H3" t="n">
-        <v>284.4395817084329</v>
+        <v>2100.567579631464</v>
       </c>
       <c r="I3" t="n">
-        <v>65.12</v>
+        <v>2100.567579631464</v>
       </c>
       <c r="J3" t="n">
-        <v>189.076520175299</v>
+        <v>2224.524099806763</v>
       </c>
       <c r="K3" t="n">
-        <v>378.2693362696824</v>
+        <v>2413.716915901147</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6197978648825</v>
+        <v>2685.067377496347</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7003396077417</v>
+        <v>2771.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>868.9806242153101</v>
+        <v>2904.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.023075899029</v>
+        <v>3143.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.552420368536</v>
+        <v>3256</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.552420368536</v>
+        <v>3081.172459504566</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.791008962092</v>
+        <v>2932.411048098123</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.554645361474</v>
+        <v>2865.174684497505</v>
       </c>
       <c r="T3" t="n">
-        <v>999.1427613033796</v>
+        <v>2859.76280043941</v>
       </c>
       <c r="U3" t="n">
-        <v>998.9302766971304</v>
+        <v>2859.550315833161</v>
       </c>
       <c r="V3" t="n">
-        <v>984.2730371097363</v>
+        <v>2844.893076245767</v>
       </c>
       <c r="W3" t="n">
-        <v>951.5728927563741</v>
+        <v>2812.192931892404</v>
       </c>
       <c r="X3" t="n">
-        <v>931.509519579215</v>
+        <v>2792.129558715245</v>
       </c>
       <c r="Y3" t="n">
-        <v>528.0838703204934</v>
+        <v>2792.129558715245</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>611.3615394356856</v>
+        <v>688.2581617439414</v>
       </c>
       <c r="C4" t="n">
-        <v>737.3635452541214</v>
+        <v>814.2601675623772</v>
       </c>
       <c r="D4" t="n">
-        <v>737.3635452541214</v>
+        <v>927.5793116873773</v>
       </c>
       <c r="E4" t="n">
-        <v>855.1924494655344</v>
+        <v>1045.40821589879</v>
       </c>
       <c r="F4" t="n">
-        <v>855.1924494655344</v>
+        <v>1045.40821589879</v>
       </c>
       <c r="G4" t="n">
-        <v>855.1924494655344</v>
+        <v>1045.40821589879</v>
       </c>
       <c r="H4" t="n">
-        <v>1024.709034624932</v>
+        <v>1214.924801058188</v>
       </c>
       <c r="I4" t="n">
-        <v>1245.841913561015</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="J4" t="n">
-        <v>1546.422113931139</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K4" t="n">
         <v>1546.422113931139</v>
@@ -4488,19 +4488,19 @@
         <v>1546.422113931139</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1424.572001403311</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1251.657783957165</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.503122964673</v>
+        <v>1008.783476806645</v>
       </c>
       <c r="P4" t="n">
-        <v>724.1517115219688</v>
+        <v>718.4320653639402</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.0211393749001</v>
+        <v>389.3014932168714</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4512,19 +4512,19 @@
         <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>348.9214477324598</v>
+        <v>205.7885129320259</v>
       </c>
       <c r="V4" t="n">
-        <v>348.9214477324598</v>
+        <v>404.6099058179719</v>
       </c>
       <c r="W4" t="n">
-        <v>348.9214477324598</v>
+        <v>576.5008240776493</v>
       </c>
       <c r="X4" t="n">
-        <v>499.9522387566533</v>
+        <v>576.5008240776493</v>
       </c>
       <c r="Y4" t="n">
-        <v>611.3615394356856</v>
+        <v>576.5008240776493</v>
       </c>
     </row>
     <row r="5">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1106.448124213083</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C5" t="n">
         <v>652.4333987151097</v>
@@ -4561,22 +4561,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>1155.766108953703</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L5" t="n">
-        <v>1677.004444444444</v>
+        <v>1237.50982862734</v>
       </c>
       <c r="M5" t="n">
-        <v>1660.642222222222</v>
+        <v>1742.368735605133</v>
       </c>
       <c r="N5" t="n">
-        <v>1644.28</v>
+        <v>2351.677689563671</v>
       </c>
       <c r="O5" t="n">
-        <v>2450.14</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P5" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
@@ -4585,25 +4585,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2906.781043807457</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2624.67476643069</v>
+        <v>2314.179446101837</v>
       </c>
       <c r="U5" t="n">
-        <v>2372.936083048255</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V5" t="n">
-        <v>2140.763331364595</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W5" t="n">
-        <v>1899.982042494951</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X5" t="n">
-        <v>1705.757968292256</v>
+        <v>991.2222439229986</v>
       </c>
       <c r="Y5" t="n">
-        <v>1593.316117097502</v>
+        <v>878.7803927282447</v>
       </c>
     </row>
     <row r="6">
@@ -4616,16 +4616,16 @@
         <v>931.509519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>566.7621332706096</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>215.3099242830312</v>
+        <v>740.2832657544849</v>
       </c>
       <c r="E6" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="F6" t="n">
-        <v>65.12</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="G6" t="n">
         <v>65.12</v>
@@ -4692,37 +4692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410.4906232651233</v>
+        <v>798.6225956808054</v>
       </c>
       <c r="C7" t="n">
-        <v>536.4926290835591</v>
+        <v>924.6246014992412</v>
       </c>
       <c r="D7" t="n">
-        <v>649.8117732085592</v>
+        <v>1037.943745624241</v>
       </c>
       <c r="E7" t="n">
-        <v>767.6406774199722</v>
+        <v>1155.772649835654</v>
       </c>
       <c r="F7" t="n">
-        <v>892.0016500119077</v>
+        <v>1155.772649835654</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898793</v>
+        <v>1155.772649835654</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058191</v>
+        <v>1325.289234995052</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994274</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994274</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931142</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931142</v>
+        <v>1522.636630943479</v>
       </c>
       <c r="M7" t="n">
         <v>1430.29164756134</v>
@@ -4743,25 +4743,25 @@
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>187.3239849197989</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>187.3239849197989</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="V7" t="n">
-        <v>187.3239849197989</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="W7" t="n">
-        <v>187.3239849197989</v>
+        <v>425.0865974184823</v>
       </c>
       <c r="X7" t="n">
-        <v>187.3239849197989</v>
+        <v>576.1173884426757</v>
       </c>
       <c r="Y7" t="n">
-        <v>298.7332855988312</v>
+        <v>687.526689121708</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1199.993207924634</v>
+        <v>298.3673161322752</v>
       </c>
       <c r="C8" t="n">
-        <v>1150.018886467064</v>
+        <v>248.3929946747056</v>
       </c>
       <c r="D8" t="n">
-        <v>1139.575294810651</v>
+        <v>237.9494030182917</v>
       </c>
       <c r="E8" t="n">
-        <v>731.1275275309853</v>
+        <v>233.5420397790304</v>
       </c>
       <c r="F8" t="n">
-        <v>726.1885086340036</v>
+        <v>228.6030208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>628.8480993800122</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4795,52 +4795,52 @@
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>448.0120508495621</v>
+        <v>229.8003143513576</v>
       </c>
       <c r="K8" t="n">
-        <v>741.0033264140374</v>
+        <v>937.5543724554984</v>
       </c>
       <c r="L8" t="n">
-        <v>724.641104191815</v>
+        <v>1743.414372455498</v>
       </c>
       <c r="M8" t="n">
-        <v>1229.500011169608</v>
+        <v>2248.273279433291</v>
       </c>
       <c r="N8" t="n">
-        <v>1213.137788947386</v>
+        <v>2857.58223339183</v>
       </c>
       <c r="O8" t="n">
-        <v>2018.997788947386</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P8" t="n">
-        <v>2824.857788947386</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S8" t="n">
-        <v>2906.781043807457</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T8" t="n">
-        <v>2718.219850142241</v>
+        <v>2163.551768150619</v>
       </c>
       <c r="U8" t="n">
-        <v>2466.481166759806</v>
+        <v>1911.813084768184</v>
       </c>
       <c r="V8" t="n">
-        <v>2234.308415076146</v>
+        <v>1275.599929044119</v>
       </c>
       <c r="W8" t="n">
-        <v>1993.527126206502</v>
+        <v>687.8608303737385</v>
       </c>
       <c r="X8" t="n">
-        <v>1799.303052003807</v>
+        <v>493.6367561710438</v>
       </c>
       <c r="Y8" t="n">
-        <v>1686.861200809053</v>
+        <v>381.1949049762899</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123.4287114984069</v>
+        <v>762.705640524864</v>
       </c>
       <c r="C9" t="n">
-        <v>123.4287114984069</v>
+        <v>762.705640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>123.4287114984069</v>
+        <v>411.2534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>123.4287114984069</v>
+        <v>65.12</v>
       </c>
       <c r="F9" t="n">
-        <v>123.4287114984069</v>
+        <v>65.12</v>
       </c>
       <c r="G9" t="n">
-        <v>123.4287114984069</v>
+        <v>65.12</v>
       </c>
       <c r="H9" t="n">
-        <v>123.4287114984069</v>
+        <v>65.12</v>
       </c>
       <c r="I9" t="n">
         <v>65.12</v>
@@ -4898,28 +4898,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>667.7506049216878</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>600.5142413210704</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>191.0619532225715</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>190.8494686163223</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>176.1922290289282</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>143.492084675566</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>123.4287114984069</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>123.4287114984069</v>
+        <v>762.705640524864</v>
       </c>
     </row>
     <row r="10">
@@ -4929,37 +4929,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1058.740229061081</v>
+        <v>911.1945562607825</v>
       </c>
       <c r="C10" t="n">
-        <v>1058.740229061081</v>
+        <v>911.1945562607825</v>
       </c>
       <c r="D10" t="n">
-        <v>1058.740229061081</v>
+        <v>911.1945562607825</v>
       </c>
       <c r="E10" t="n">
-        <v>1058.740229061081</v>
+        <v>1029.023460472195</v>
       </c>
       <c r="F10" t="n">
-        <v>1058.740229061081</v>
+        <v>1029.023460472195</v>
       </c>
       <c r="G10" t="n">
-        <v>1058.740229061081</v>
+        <v>1182.430026359081</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058194</v>
+        <v>1182.430026359081</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994277</v>
+        <v>1182.430026359081</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994277</v>
+        <v>1436.057679994261</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931129</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.422113931145</v>
+        <v>1546.422113931129</v>
       </c>
       <c r="M10" t="n">
         <v>1430.29164756134</v>
@@ -4989,16 +4989,16 @@
         <v>536.9971268912645</v>
       </c>
       <c r="V10" t="n">
-        <v>735.8185197772104</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="W10" t="n">
-        <v>907.7094380368878</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="X10" t="n">
-        <v>1058.740229061081</v>
+        <v>688.027917915458</v>
       </c>
       <c r="Y10" t="n">
-        <v>1058.740229061081</v>
+        <v>799.4372185944903</v>
       </c>
     </row>
     <row r="11">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1020.164977321635</v>
+        <v>1026.201205738787</v>
       </c>
       <c r="C11" t="n">
-        <v>793.4229790963881</v>
+        <v>799.4592075135407</v>
       </c>
       <c r="D11" t="n">
-        <v>793.4229790963881</v>
+        <v>612.24793908945</v>
       </c>
       <c r="E11" t="n">
         <v>612.24793908945</v>
@@ -5035,19 +5035,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>456.4291130376557</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L11" t="n">
-        <v>456.4291130376557</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>967.2779417665907</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>1580.498261541354</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2011.540904947332</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>2817.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3256</v>
+        <v>3229.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3194.957276104898</v>
+        <v>2957.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>3194.957276104898</v>
+        <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2766.450915954786</v>
+        <v>2163.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>2357.510487503449</v>
+        <v>1754.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>1939.961521866128</v>
+        <v>1336.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1568.969770895757</v>
+        <v>1285.796471350479</v>
       </c>
       <c r="Y11" t="n">
-        <v>1279.760242933326</v>
+        <v>1285.796471350479</v>
       </c>
     </row>
     <row r="12">
@@ -5117,16 +5117,16 @@
         <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2452.317953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5166,52 +5166,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="C13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="D13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="E13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="F13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="G13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="H13" t="n">
-        <v>173.6223697938169</v>
+        <v>175.0090463985742</v>
       </c>
       <c r="I13" t="n">
-        <v>221.5052487298998</v>
+        <v>222.8919253346571</v>
       </c>
       <c r="J13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="K13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="L13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="M13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="N13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="O13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="P13" t="n">
-        <v>409.3389893823512</v>
+        <v>410.7256659871084</v>
       </c>
       <c r="Q13" t="n">
-        <v>409.3389893823512</v>
+        <v>65.12</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5229,13 +5229,13 @@
         <v>178.8182646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="X13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="Y13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
     </row>
     <row r="14">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>653.4059340138207</v>
+        <v>895.5001121224765</v>
       </c>
       <c r="C14" t="n">
-        <v>653.4059340138207</v>
+        <v>695.0207401598564</v>
       </c>
       <c r="D14" t="n">
-        <v>492.4572918523562</v>
+        <v>534.0720979983919</v>
       </c>
       <c r="E14" t="n">
         <v>379.1596842540801</v>
@@ -5269,22 +5269,22 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K14" t="n">
-        <v>887.4717564436343</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L14" t="n">
-        <v>887.4717564436343</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M14" t="n">
-        <v>1398.320585172569</v>
+        <v>1580.686366347869</v>
       </c>
       <c r="N14" t="n">
+        <v>1580.686366347869</v>
+      </c>
+      <c r="O14" t="n">
         <v>2011.540904947332</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2817.400904947332</v>
       </c>
       <c r="P14" t="n">
         <v>2817.400904947332</v>
@@ -5308,13 +5308,13 @@
         <v>1885.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1494.414599770435</v>
+        <v>1736.508777879091</v>
       </c>
       <c r="X14" t="n">
-        <v>1149.68547506269</v>
+        <v>1391.779653171346</v>
       </c>
       <c r="Y14" t="n">
-        <v>886.7385733628859</v>
+        <v>1128.832751471542</v>
       </c>
     </row>
     <row r="15">
@@ -5354,13 +5354,13 @@
         <v>660.2942142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>931.6446758324473</v>
+        <v>1096.180984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1266.215217575306</v>
+        <v>1430.751526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1647.985502182875</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
         <v>2051.564262473451</v>
@@ -5448,7 +5448,7 @@
         <v>599.0397446017254</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>119.4041219496062</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
         <v>321.4503343338824</v>
@@ -5509,22 +5509,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.135479385524</v>
+        <v>520.2108514963016</v>
       </c>
       <c r="L17" t="n">
-        <v>1166.135479385524</v>
+        <v>1326.070851496302</v>
       </c>
       <c r="M17" t="n">
-        <v>1676.984308114459</v>
+        <v>1836.919680225237</v>
       </c>
       <c r="N17" t="n">
-        <v>2011.540904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.540904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5533,25 +5533,25 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5582,28 +5582,28 @@
         <v>65.12</v>
       </c>
       <c r="I18" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J18" t="n">
-        <v>250.3313981428639</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>439.5242142372473</v>
+        <v>422.2896261621044</v>
       </c>
       <c r="L18" t="n">
-        <v>987.0846758324475</v>
+        <v>693.6400877573045</v>
       </c>
       <c r="M18" t="n">
-        <v>1073.165217575307</v>
+        <v>779.7206295001638</v>
       </c>
       <c r="N18" t="n">
-        <v>1206.445502182875</v>
+        <v>1189.210914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5673,19 +5673,19 @@
         <v>713.2950178022188</v>
       </c>
       <c r="M19" t="n">
-        <v>469.2226830521684</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="N19" t="n">
-        <v>174.0862433837998</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="O19" t="n">
-        <v>65.12</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="P19" t="n">
-        <v>65.12</v>
+        <v>300.721384137292</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.12</v>
+        <v>300.721384137292</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5743,25 +5743,25 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>1580.686366347868</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>1580.686366347869</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>2011.540904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>2011.540904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P20" t="n">
-        <v>2817.400904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5819,22 +5819,22 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>869.8480986016793</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>864.9885601968793</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>951.0691019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1084.349386547307</v>
       </c>
       <c r="O21" t="n">
         <v>1599.601838231026</v>
@@ -5883,46 +5883,46 @@
         <v>428.7519797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>428.7519797853442</v>
+        <v>422.1497393251871</v>
       </c>
       <c r="E22" t="n">
-        <v>428.7519797853442</v>
+        <v>420.1488253484633</v>
       </c>
       <c r="F22" t="n">
-        <v>433.3229523772797</v>
+        <v>424.7197979403988</v>
       </c>
       <c r="G22" t="n">
-        <v>466.939518264165</v>
+        <v>458.3363638272841</v>
       </c>
       <c r="H22" t="n">
-        <v>516.6661034235625</v>
+        <v>508.0629489866817</v>
       </c>
       <c r="I22" t="n">
-        <v>618.0089823596454</v>
+        <v>609.4058279227646</v>
       </c>
       <c r="J22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="K22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="L22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="M22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="N22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="O22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="P22" t="n">
-        <v>516.472794369291</v>
+        <v>850.6995685752159</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602765154</v>
       </c>
       <c r="C23" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165967236</v>
       </c>
       <c r="D23" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180874</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172566039</v>
       </c>
       <c r="F23" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761374</v>
       </c>
       <c r="G23" t="n">
-        <v>195.4327865692196</v>
+        <v>194.9978283727372</v>
       </c>
       <c r="H23" t="n">
         <v>65.12</v>
@@ -5983,19 +5983,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>887.4717564436343</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>887.4717564436343</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1398.320585172569</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N23" t="n">
+        <v>1580.498261541354</v>
+      </c>
+      <c r="O23" t="n">
         <v>2011.540904947332</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2817.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>2817.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256</v>
+        <v>3256.000000000069</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3037.97154767449</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.188131787052</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.227226182395</v>
       </c>
       <c r="V23" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276512</v>
       </c>
       <c r="W23" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184645</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759729</v>
       </c>
       <c r="Y23" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342752</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>65.12</v>
       </c>
       <c r="I24" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J24" t="n">
-        <v>250.3313981428639</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>439.5242142372473</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>710.8746758324473</v>
+        <v>925.8297978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>951.0691019397386</v>
+        <v>1011.910339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>1084.349386547307</v>
+        <v>1421.40062421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1323.391838231026</v>
+        <v>1660.443075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6144,25 +6144,25 @@
         <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>859.3027230120967</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="M25" t="n">
-        <v>859.3027230120967</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="N25" t="n">
-        <v>564.1662833437281</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="O25" t="n">
-        <v>199.0697539709857</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="P25" t="n">
-        <v>149.3356360634903</v>
+        <v>300.721384137292</v>
       </c>
       <c r="Q25" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="R25" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S25" t="n">
         <v>65.12</v>
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>288.5819982252464</v>
+        <v>670.7138907336723</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>611.9330040956872</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>424.7217356715965</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>243.5466956646584</v>
       </c>
       <c r="F26" t="n">
         <v>61.84</v>
@@ -6217,25 +6217,25 @@
         <v>61.84</v>
       </c>
       <c r="J26" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>771.5463663478683</v>
+        <v>1050.61117127101</v>
       </c>
       <c r="L26" t="n">
-        <v>1536.816366347868</v>
+        <v>1050.61117127101</v>
       </c>
       <c r="M26" t="n">
-        <v>2047.665195076803</v>
+        <v>1561.459999999945</v>
       </c>
       <c r="N26" t="n">
-        <v>2047.665195076803</v>
+        <v>1561.459999999945</v>
       </c>
       <c r="O26" t="n">
-        <v>2812.93519507683</v>
+        <v>2326.729999999973</v>
       </c>
       <c r="P26" t="n">
-        <v>2812.93519507683</v>
+        <v>3092</v>
       </c>
       <c r="Q26" t="n">
         <v>3092</v>
@@ -6256,13 +6256,13 @@
         <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1208.37854276974</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="X26" t="n">
-        <v>837.3867917993684</v>
+        <v>1219.518684307795</v>
       </c>
       <c r="Y26" t="n">
-        <v>548.1772638369378</v>
+        <v>930.3091563453638</v>
       </c>
     </row>
     <row r="27">
@@ -6305,13 +6305,13 @@
         <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.213656412845</v>
+        <v>2449.037953866594</v>
       </c>
       <c r="P27" t="n">
         <v>2580.493000882351</v>
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>175.0042331365846</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="C28" t="n">
-        <v>126.7969132900749</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="D28" t="n">
-        <v>65.64921828446326</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="E28" t="n">
-        <v>65.64921828446326</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="F28" t="n">
-        <v>65.64921828446326</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="G28" t="n">
-        <v>65.64921828446326</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="H28" t="n">
+        <v>171.7290463985742</v>
+      </c>
+      <c r="I28" t="n">
+        <v>219.6119253346571</v>
+      </c>
+      <c r="J28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="K28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="L28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="M28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="N28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="O28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="P28" t="n">
+        <v>407.4456659871084</v>
+      </c>
+      <c r="Q28" t="n">
         <v>61.84</v>
       </c>
-      <c r="I28" t="n">
-        <v>109.7228789360829</v>
-      </c>
-      <c r="J28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="K28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="L28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="M28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="N28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="O28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="P28" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>297.5566195885342</v>
-      </c>
       <c r="R28" t="n">
-        <v>297.5566195885342</v>
+        <v>61.84</v>
       </c>
       <c r="S28" t="n">
-        <v>211.2005224488586</v>
+        <v>61.84</v>
       </c>
       <c r="T28" t="n">
-        <v>226.0262016076634</v>
+        <v>76.66567915880486</v>
       </c>
       <c r="U28" t="n">
-        <v>299.3273942459501</v>
+        <v>149.9668717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>324.898787131896</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>323.5121105271388</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="X28" t="n">
-        <v>300.8417616078382</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="Y28" t="n">
-        <v>237.7454455982802</v>
+        <v>175.5382646830375</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>512.760190708043</v>
+        <v>1204.096245745725</v>
       </c>
       <c r="C29" t="n">
-        <v>286.0181924827966</v>
+        <v>977.3542475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>98.80692405870585</v>
+        <v>790.1429790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6460,16 +6460,16 @@
         <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>453.1491130376558</v>
+        <v>764.0617564435998</v>
       </c>
       <c r="M29" t="n">
-        <v>963.9979417665908</v>
+        <v>1274.910585172535</v>
       </c>
       <c r="N29" t="n">
-        <v>1577.218261541354</v>
+        <v>1888.130904947298</v>
       </c>
       <c r="O29" t="n">
-        <v>1888.130904947298</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2653.400904947332</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T29" t="n">
-        <v>2427.957223879615</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U29" t="n">
-        <v>1999.450863729503</v>
+        <v>2272.024770600536</v>
       </c>
       <c r="V29" t="n">
-        <v>1590.510435278166</v>
+        <v>2272.024770600536</v>
       </c>
       <c r="W29" t="n">
-        <v>1172.961469640845</v>
+        <v>1854.475804963215</v>
       </c>
       <c r="X29" t="n">
-        <v>801.9697186704736</v>
+        <v>1483.484053992844</v>
       </c>
       <c r="Y29" t="n">
-        <v>512.760190708043</v>
+        <v>1204.096245745725</v>
       </c>
     </row>
     <row r="30">
@@ -6533,19 +6533,19 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O30" t="n">
         <v>2245.213656412845</v>
@@ -6594,34 +6594,34 @@
         <v>174.1515880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="E31" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="F31" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="G31" t="n">
-        <v>174.1515880782802</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="H31" t="n">
-        <v>170.342369793817</v>
+        <v>113.0038930726686</v>
       </c>
       <c r="I31" t="n">
-        <v>218.2252487298999</v>
+        <v>160.8867720087515</v>
       </c>
       <c r="J31" t="n">
-        <v>406.0589893823512</v>
+        <v>348.7205126612029</v>
       </c>
       <c r="K31" t="n">
-        <v>406.0589893823512</v>
+        <v>348.7205126612029</v>
       </c>
       <c r="L31" t="n">
-        <v>406.0589893823512</v>
+        <v>348.7205126612029</v>
       </c>
       <c r="M31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="N31" t="n">
         <v>61.84</v>
@@ -6694,22 +6694,22 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K32" t="n">
-        <v>1155.056868702879</v>
+        <v>1155.05686870288</v>
       </c>
       <c r="L32" t="n">
-        <v>1920.326868702878</v>
+        <v>1920.32686870288</v>
       </c>
       <c r="M32" t="n">
-        <v>1925.839809149367</v>
+        <v>1904.788787894799</v>
       </c>
       <c r="N32" t="n">
-        <v>1910.301728341285</v>
+        <v>2514.921883267477</v>
       </c>
       <c r="O32" t="n">
-        <v>1894.763647533204</v>
+        <v>2499.383802459396</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6718,22 +6718,22 @@
         <v>3092</v>
       </c>
       <c r="S32" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T32" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U32" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V32" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W32" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X32" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y32" t="n">
         <v>997.0248446907499</v>
@@ -6767,22 +6767,22 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>448.1242142372473</v>
+        <v>663.0793362696824</v>
       </c>
       <c r="L33" t="n">
-        <v>719.4746758324475</v>
+        <v>934.4297978648824</v>
       </c>
       <c r="M33" t="n">
-        <v>1030.300920121557</v>
+        <v>1020.510339607742</v>
       </c>
       <c r="N33" t="n">
-        <v>1163.581204729126</v>
+        <v>1153.79062421531</v>
       </c>
       <c r="O33" t="n">
         <v>1402.623656412844</v>
@@ -6855,22 +6855,22 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630703</v>
+        <v>745.3076490908711</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630703</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="O34" t="n">
-        <v>1011.831843630703</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="P34" t="n">
-        <v>941.0737317239891</v>
+        <v>61.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
         <v>523.4763124297214</v>
@@ -6931,22 +6931,22 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.9405883765177</v>
+        <v>1154.134391781985</v>
       </c>
       <c r="L35" t="n">
-        <v>415.4025075684368</v>
+        <v>1210.913856235339</v>
       </c>
       <c r="M35" t="n">
-        <v>921.0855559603705</v>
+        <v>1716.596904627273</v>
       </c>
       <c r="N35" t="n">
-        <v>1129.493647533147</v>
+        <v>2326.729999999951</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533196</v>
+        <v>3092</v>
       </c>
       <c r="P35" t="n">
-        <v>2660.033647533245</v>
+        <v>3076.461919191918</v>
       </c>
       <c r="Q35" t="n">
         <v>3092</v>
@@ -6973,7 +6973,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,28 +7004,28 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>448.1242142372473</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>719.4746758324475</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>805.5552175753068</v>
+        <v>1020.510339607742</v>
       </c>
       <c r="N36" t="n">
-        <v>938.8355021828751</v>
+        <v>1280.322732289551</v>
       </c>
       <c r="O36" t="n">
-        <v>1402.623656412844</v>
+        <v>1519.36518397327</v>
       </c>
       <c r="P36" t="n">
-        <v>1515.153000882351</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7092,25 +7092,25 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>877.945350542037</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M37" t="n">
-        <v>645.9942279131988</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>362.9790003660423</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O37" t="n">
-        <v>362.9790003660423</v>
+        <v>902.2945710196249</v>
       </c>
       <c r="P37" t="n">
-        <v>362.9790003660423</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="Q37" t="n">
-        <v>362.9790003660423</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R37" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
         <v>644.0209141871454</v>
@@ -7165,22 +7165,22 @@
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>445.5561922637023</v>
+        <v>61.84</v>
       </c>
       <c r="K38" t="n">
-        <v>809.1011884638447</v>
+        <v>61.84</v>
       </c>
       <c r="L38" t="n">
-        <v>794.4855845766601</v>
+        <v>827.1099999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>1300.168632968594</v>
+        <v>1332.793048391934</v>
       </c>
       <c r="N38" t="n">
-        <v>1910.301728341272</v>
+        <v>1942.926143764612</v>
       </c>
       <c r="O38" t="n">
-        <v>2675.571728341328</v>
+        <v>1927.38806295653</v>
       </c>
       <c r="P38" t="n">
         <v>2660.033647533246</v>
@@ -7210,7 +7210,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7244,25 +7244,25 @@
         <v>61.84</v>
       </c>
       <c r="J39" t="n">
-        <v>185.796520175299</v>
+        <v>312.3286282495399</v>
       </c>
       <c r="K39" t="n">
-        <v>384.7799167834979</v>
+        <v>501.5214443439232</v>
       </c>
       <c r="L39" t="n">
-        <v>656.130378378698</v>
+        <v>1060.961905939123</v>
       </c>
       <c r="M39" t="n">
-        <v>1030.300920121557</v>
+        <v>1147.042447681983</v>
       </c>
       <c r="N39" t="n">
-        <v>1163.581204729126</v>
+        <v>1280.322732289551</v>
       </c>
       <c r="O39" t="n">
-        <v>1402.623656412844</v>
+        <v>1519.36518397327</v>
       </c>
       <c r="P39" t="n">
-        <v>1515.153000882351</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q39" t="n">
         <v>1631.894528442776</v>
@@ -7329,25 +7329,25 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.831843630703</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M40" t="n">
-        <v>779.8807210018645</v>
+        <v>877.945350542037</v>
       </c>
       <c r="N40" t="n">
-        <v>496.865493454708</v>
+        <v>877.945350542037</v>
       </c>
       <c r="O40" t="n">
-        <v>143.8901762031777</v>
+        <v>524.9700332905068</v>
       </c>
       <c r="P40" t="n">
-        <v>61.84</v>
+        <v>524.9700332905068</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1084.139304041668</v>
+        <v>886.016157451241</v>
       </c>
       <c r="C41" t="n">
-        <v>845.2760936952099</v>
+        <v>647.1529471047825</v>
       </c>
       <c r="D41" t="n">
-        <v>645.943613149907</v>
+        <v>447.8204665594797</v>
       </c>
       <c r="E41" t="n">
-        <v>452.6473610217569</v>
+        <v>254.5242144313295</v>
       </c>
       <c r="F41" t="n">
-        <v>258.8194532358863</v>
+        <v>254.5242144313295</v>
       </c>
       <c r="G41" t="n">
-        <v>258.8194532358863</v>
+        <v>61.84</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7408,16 +7408,16 @@
         <v>1162.855479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>1928.125479385524</v>
+        <v>1377.282076218334</v>
       </c>
       <c r="M41" t="n">
-        <v>1928.125479385524</v>
+        <v>1888.130904947269</v>
       </c>
       <c r="N41" t="n">
-        <v>2541.345799160287</v>
+        <v>1888.130904947269</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947269</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7429,25 +7429,25 @@
         <v>3092</v>
       </c>
       <c r="S41" t="n">
-        <v>2807.304881007754</v>
+        <v>3092</v>
       </c>
       <c r="T41" t="n">
-        <v>2807.304881007754</v>
+        <v>2714.549917445895</v>
       </c>
       <c r="U41" t="n">
-        <v>2366.67730873643</v>
+        <v>2273.922345174571</v>
       </c>
       <c r="V41" t="n">
-        <v>2366.67730873643</v>
+        <v>2271.846516117904</v>
       </c>
       <c r="W41" t="n">
-        <v>1937.007130977898</v>
+        <v>1842.176338359371</v>
       </c>
       <c r="X41" t="n">
-        <v>1657.186521858215</v>
+        <v>1459.063375267787</v>
       </c>
       <c r="Y41" t="n">
-        <v>1355.855781774572</v>
+        <v>1157.732635184145</v>
       </c>
     </row>
     <row r="42">
@@ -7481,31 +7481,31 @@
         <v>61.84</v>
       </c>
       <c r="J42" t="n">
-        <v>396.666520175299</v>
+        <v>195.3121874480754</v>
       </c>
       <c r="K42" t="n">
-        <v>796.7293362696823</v>
+        <v>595.3750035424589</v>
       </c>
       <c r="L42" t="n">
-        <v>1278.949797864882</v>
+        <v>1077.595465137659</v>
       </c>
       <c r="M42" t="n">
-        <v>1575.900339607742</v>
+        <v>1374.546006880518</v>
       </c>
       <c r="N42" t="n">
-        <v>1866.192460435216</v>
+        <v>1718.696291488086</v>
       </c>
       <c r="O42" t="n">
-        <v>2316.104912118934</v>
+        <v>2168.608743171805</v>
       </c>
       <c r="P42" t="n">
-        <v>2639.504256588441</v>
+        <v>2492.008087641312</v>
       </c>
       <c r="Q42" t="n">
-        <v>2679.025784148866</v>
+        <v>2531.529615201737</v>
       </c>
       <c r="R42" t="n">
-        <v>2341.375483853533</v>
+        <v>2480.230476522543</v>
       </c>
       <c r="S42" t="n">
         <v>2224.105224033037</v>
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="C43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="D43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="H43" t="n">
+        <v>139.8982646830375</v>
+      </c>
+      <c r="I43" t="n">
+        <v>175.9011436191204</v>
+      </c>
+      <c r="J43" t="n">
+        <v>351.8548842715717</v>
+      </c>
+      <c r="K43" t="n">
+        <v>351.8548842715717</v>
+      </c>
+      <c r="L43" t="n">
+        <v>139.1805123950271</v>
+      </c>
+      <c r="M43" t="n">
+        <v>139.1805123950271</v>
+      </c>
+      <c r="N43" t="n">
+        <v>139.1805123950271</v>
+      </c>
+      <c r="O43" t="n">
+        <v>139.1805123950271</v>
+      </c>
+      <c r="P43" t="n">
         <v>61.84</v>
       </c>
-      <c r="I43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="J43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="K43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="L43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="M43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="N43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="O43" t="n">
-        <v>91.27831913164476</v>
-      </c>
-      <c r="P43" t="n">
-        <v>91.27831913164476</v>
-      </c>
       <c r="Q43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="S43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>91.27831913164476</v>
+        <v>64.78567915880487</v>
       </c>
       <c r="U43" t="n">
-        <v>91.27831913164476</v>
+        <v>126.2068717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>91.27831913164476</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="X43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="Y43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>311.4230884585372</v>
+        <v>692.5675514511847</v>
       </c>
       <c r="C44" t="n">
-        <v>61.84</v>
+        <v>692.5675514511847</v>
       </c>
       <c r="D44" t="n">
-        <v>61.84</v>
+        <v>466.9724446432556</v>
       </c>
       <c r="E44" t="n">
-        <v>61.84</v>
+        <v>466.9724446432556</v>
       </c>
       <c r="F44" t="n">
-        <v>61.84</v>
+        <v>466.9724446432556</v>
       </c>
       <c r="G44" t="n">
-        <v>61.84</v>
+        <v>285.0820794985125</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7642,19 +7642,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K44" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>764.0617564435566</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>1274.910585172492</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="N44" t="n">
-        <v>1888.130904947255</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="O44" t="n">
-        <v>1888.130904947255</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3027.476162799703</v>
+        <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>2716.518417544831</v>
+        <v>3092</v>
       </c>
       <c r="T44" t="n">
-        <v>2716.518417544831</v>
+        <v>2688.287291183269</v>
       </c>
       <c r="U44" t="n">
-        <v>2249.628219010881</v>
+        <v>2221.397092649318</v>
       </c>
       <c r="V44" t="n">
-        <v>1802.303952175705</v>
+        <v>1774.072825814143</v>
       </c>
       <c r="W44" t="n">
-        <v>1346.371148154546</v>
+        <v>1318.140021792984</v>
       </c>
       <c r="X44" t="n">
-        <v>936.9955588003362</v>
+        <v>1318.140021792984</v>
       </c>
       <c r="Y44" t="n">
-        <v>609.4021924540671</v>
+        <v>990.5466554467146</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1028.890452379605</v>
+        <v>570.1625524655966</v>
       </c>
       <c r="C45" t="n">
-        <v>853.031954959888</v>
+        <v>394.3040550458801</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>394.3040550458801</v>
       </c>
       <c r="E45" t="n">
-        <v>533.2240922128019</v>
+        <v>237.0595123974836</v>
       </c>
       <c r="F45" t="n">
-        <v>379.04606964929</v>
+        <v>237.0595123974836</v>
       </c>
       <c r="G45" t="n">
-        <v>238.9051243209795</v>
+        <v>208.4744315014355</v>
       </c>
       <c r="H45" t="n">
-        <v>92.27069281954398</v>
+        <v>61.84</v>
       </c>
       <c r="I45" t="n">
         <v>61.84</v>
@@ -7721,49 +7721,49 @@
         <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>745.2493362696823</v>
+        <v>719.5546261839681</v>
       </c>
       <c r="L45" t="n">
-        <v>1201.729797864882</v>
+        <v>1176.035087779168</v>
       </c>
       <c r="M45" t="n">
-        <v>1472.940339607742</v>
+        <v>1447.245629522027</v>
       </c>
       <c r="N45" t="n">
-        <v>1647.552918863993</v>
+        <v>1765.655914129596</v>
       </c>
       <c r="O45" t="n">
-        <v>2071.725370547711</v>
+        <v>2004.698365813314</v>
       </c>
       <c r="P45" t="n">
-        <v>2369.384715017218</v>
+        <v>2302.357710282821</v>
       </c>
       <c r="Q45" t="n">
-        <v>2383.166242577644</v>
+        <v>2316.139237843247</v>
       </c>
       <c r="R45" t="n">
-        <v>2383.166242577644</v>
+        <v>1952.226311285287</v>
       </c>
       <c r="S45" t="n">
-        <v>2383.166242577644</v>
+        <v>1669.838432533155</v>
       </c>
       <c r="T45" t="n">
-        <v>2162.602843368034</v>
+        <v>1449.275033323545</v>
       </c>
       <c r="U45" t="n">
-        <v>1947.238843610269</v>
+        <v>1449.275033323545</v>
       </c>
       <c r="V45" t="n">
-        <v>1717.43008887136</v>
+        <v>1219.466278584636</v>
       </c>
       <c r="W45" t="n">
-        <v>1678.194178498644</v>
+        <v>1219.466278584636</v>
       </c>
       <c r="X45" t="n">
-        <v>1442.979290169969</v>
+        <v>984.2513902559613</v>
       </c>
       <c r="Y45" t="n">
-        <v>1228.442529800137</v>
+        <v>769.7146298861286</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="H46" t="n">
+        <v>85.22794999564401</v>
+      </c>
+      <c r="I46" t="n">
+        <v>95.49082893172692</v>
+      </c>
+      <c r="J46" t="n">
+        <v>245.7045695841782</v>
+      </c>
+      <c r="K46" t="n">
+        <v>245.7045695841782</v>
+      </c>
+      <c r="L46" t="n">
+        <v>245.7045695841782</v>
+      </c>
+      <c r="M46" t="n">
+        <v>245.7045695841782</v>
+      </c>
+      <c r="N46" t="n">
+        <v>245.7045695841782</v>
+      </c>
+      <c r="O46" t="n">
         <v>61.84</v>
       </c>
-      <c r="I46" t="n">
-        <v>72.10287893608292</v>
-      </c>
-      <c r="J46" t="n">
-        <v>139.5834371960531</v>
-      </c>
-      <c r="K46" t="n">
-        <v>139.5834371960531</v>
-      </c>
-      <c r="L46" t="n">
-        <v>139.5834371960531</v>
-      </c>
-      <c r="M46" t="n">
-        <v>139.5834371960531</v>
-      </c>
-      <c r="N46" t="n">
-        <v>139.5834371960531</v>
-      </c>
-      <c r="O46" t="n">
-        <v>139.5834371960531</v>
-      </c>
       <c r="P46" t="n">
-        <v>139.5834371960531</v>
+        <v>61.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>139.5834371960531</v>
+        <v>61.84</v>
       </c>
       <c r="R46" t="n">
-        <v>139.5834371960531</v>
+        <v>61.84</v>
       </c>
       <c r="S46" t="n">
-        <v>139.5834371960531</v>
+        <v>61.84</v>
       </c>
       <c r="T46" t="n">
-        <v>116.3262993109443</v>
+        <v>61.84</v>
       </c>
       <c r="U46" t="n">
-        <v>116.3262993109443</v>
+        <v>97.52119263828664</v>
       </c>
       <c r="V46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.22794999564401</v>
       </c>
     </row>
   </sheetData>
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>65.90862873094359</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>582.6427212635811</v>
       </c>
       <c r="O2" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814674</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8204,25 +8204,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>532.2245521358337</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>571.0933679639695</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q5" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>214.2751174529344</v>
       </c>
       <c r="K8" t="n">
-        <v>306.2599628088307</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,10 +8690,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>505.6444790750808</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,25 +8912,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O14" t="n">
-        <v>884.2478695740924</v>
+        <v>505.4544742200154</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>64.42599844307665</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>815.1849144666769</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
         <v>70.24786957409245</v>
@@ -9170,7 +9170,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>912.4555627157581</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,7 +9626,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>505.6444790750808</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>603.4970285185401</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9878,10 +9878,10 @@
         <v>843.2478695741199</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.287060040709</v>
       </c>
       <c r="Q26" t="n">
-        <v>454.7063256640203</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>314.0531751575193</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>384.3010447316117</v>
+        <v>843.2478695741272</v>
       </c>
       <c r="P29" t="n">
-        <v>773.2870600407163</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10340,22 +10340,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>773.0000000000005</v>
       </c>
       <c r="M32" t="n">
-        <v>565.102638684342</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407235</v>
+        <v>602.359795605881</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>70.68111765713381</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>698.9556687268854</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
         <v>843.2478695741418</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407308</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>203.5880843274875</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509142</v>
       </c>
       <c r="K38" t="n">
-        <v>375.292246238141</v>
+        <v>14.46944784831408</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,10 +10823,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.247869574149</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>740.9888887716313</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11051,19 +11051,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>773</v>
+        <v>216.5925220533434</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>183.4348451165624</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407454</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>314.0531751574757</v>
+        <v>773</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>773.2870600407599</v>
+        <v>732.888500002104</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22703,7 +22703,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696448846</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.662449696448334</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,10 +22937,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662449696445705</v>
+        <v>29.21007785423211</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>5.66244969644255</v>
+        <v>5.66244969645831</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23229,10 +23229,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23271,13 +23271,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>209.415871146172</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23289,10 +23289,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>316.6284851532052</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>158.6896570983607</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23463,13 +23463,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>41.19865808457531</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>239.6732363275692</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>421.8608472510409</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23888,22 +23888,22 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>253.5689831290532</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>214.3567576852319</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -24098,10 +24098,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>69.04626797189979</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>116.7176215172853</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.4306086145176096</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24231,7 +24231,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.430608614578091</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -24359,28 +24359,28 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>359.2111205998571</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>213.5938961296789</v>
       </c>
       <c r="R25" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24411,16 +24411,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>166.2815004713887</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>178.7573722870162</v>
@@ -24471,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>35.06290239760574</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
         <v>55.98090483695654</v>
@@ -24611,13 +24611,13 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>500.839266425598</v>
+        <v>158.6896570983607</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>51.88094353457656</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24629,13 +24629,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24654,16 +24654,16 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>142.7660347887499</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>9.723502518158796</v>
       </c>
     </row>
     <row r="30">
@@ -24809,7 +24809,7 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>55.98090483695654</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>11.61990386795907</v>
       </c>
       <c r="N31" t="n">
-        <v>5.408275783157251</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
@@ -25070,25 +25070,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>98.32028696589566</v>
       </c>
       <c r="N34" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>326.3973665406309</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>241.0036641940478</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>208.8479973216246</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25544,28 +25544,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>315.2182228871316</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>47.71401317085173</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,22 +25644,22 @@
         <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>373.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>414.7959534007232</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>102.2594304321818</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>283.4876499999776</v>
       </c>
       <c r="S42" t="n">
-        <v>137.4664427423198</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>75.52077380114304</v>
       </c>
       <c r="L43" t="n">
-        <v>210.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>307.6316114025499</v>
@@ -25793,7 +25793,7 @@
         <v>427.445564079015</v>
       </c>
       <c r="P43" t="n">
-        <v>474.4478973282775</v>
+        <v>397.8807900572007</v>
       </c>
       <c r="Q43" t="n">
         <v>512.839266425598</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>13.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>34.44364543010755</v>
@@ -25833,10 +25833,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>15.38732066904208</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
@@ -25845,10 +25845,10 @@
         <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>36.68591079372055</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>399.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25915,22 +25915,22 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>110.4403057879398</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>30.12638589134853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,22 +25957,22 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>360.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>213.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>206.5295916408394</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26027,7 +26027,7 @@
         <v>384.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>453.445564079015</v>
+        <v>271.4196401906785</v>
       </c>
       <c r="P46" t="n">
         <v>500.4478973282775</v>
@@ -26042,7 +26042,7 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>806633.9565937308</v>
+        <v>806633.956593731</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2809321.327899823</v>
+        <v>2809321.327899822</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3453894.020262508</v>
+        <v>3453894.020262505</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4124429.816181584</v>
+        <v>4124429.816181581</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4794965.612100662</v>
+        <v>4794965.612100659</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6074943.841322232</v>
+        <v>6074943.841322231</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6687293.845533817</v>
+        <v>6687293.845533818</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7362705.543907756</v>
+        <v>7362705.543907757</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8037020.450518644</v>
+        <v>8037020.450518647</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8711335.357129535</v>
+        <v>8711335.35712954</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9304311.398380075</v>
+        <v>9304311.398380078</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9858424.34023945</v>
+        <v>9858424.340239458</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510411.198156912</v>
+        <v>1510411.198156913</v>
       </c>
       <c r="C2" t="n">
         <v>1510411.198156912</v>
@@ -26290,7 +26290,7 @@
         <v>1462987.191096176</v>
       </c>
       <c r="I2" t="n">
-        <v>1462987.191096171</v>
+        <v>1462987.191096177</v>
       </c>
       <c r="J2" t="n">
         <v>1336036.372825283</v>
@@ -26308,7 +26308,7 @@
         <v>1471232.523514663</v>
       </c>
       <c r="O2" t="n">
-        <v>1296158.908393284</v>
+        <v>1296158.908393285</v>
       </c>
       <c r="P2" t="n">
         <v>1208973.691329537</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.1964558329</v>
+        <v>551386.5909530218</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165733</v>
+        <v>549634.6822137621</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037628</v>
+        <v>547880.3969009514</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682165</v>
+        <v>494181.5516694609</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925398</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.0458524449</v>
+        <v>517298.0248536893</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.7754680162</v>
+        <v>515622.7544692631</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335261</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795844</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.914492766</v>
+        <v>519822.4908174383</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912134</v>
+        <v>518092.3721158858</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666612</v>
+        <v>516359.7657913336</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.0841633691</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682331</v>
+        <v>393445.3182115989</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>584540.2017010793</v>
+        <v>589377.8072038908</v>
       </c>
       <c r="C6" t="n">
-        <v>872820.1104403387</v>
+        <v>877657.71594315</v>
       </c>
       <c r="D6" t="n">
-        <v>874574.3957531494</v>
+        <v>879412.0012559607</v>
       </c>
       <c r="E6" t="n">
-        <v>628133.1456070623</v>
+        <v>632921.166605818</v>
       </c>
       <c r="F6" t="n">
-        <v>815978.3280321837</v>
+        <v>820766.349030939</v>
       </c>
       <c r="G6" t="n">
-        <v>843881.7593036306</v>
+        <v>848669.7803023863</v>
       </c>
       <c r="H6" t="n">
-        <v>867954.694243731</v>
+        <v>872742.7152424863</v>
       </c>
       <c r="I6" t="n">
-        <v>869629.9646281549</v>
+        <v>874417.9856269137</v>
       </c>
       <c r="J6" t="n">
-        <v>396856.8352917572</v>
+        <v>401521.8638483914</v>
       </c>
       <c r="K6" t="n">
-        <v>786417.5769456986</v>
+        <v>791082.605502333</v>
       </c>
       <c r="L6" t="n">
-        <v>800036.1300218971</v>
+        <v>804747.5536972245</v>
       </c>
       <c r="M6" t="n">
-        <v>876966.2487234499</v>
+        <v>881677.6723987774</v>
       </c>
       <c r="N6" t="n">
-        <v>878698.8550480022</v>
+        <v>883410.2787233298</v>
       </c>
       <c r="O6" t="n">
-        <v>717937.727229915</v>
+        <v>722602.7557865498</v>
       </c>
       <c r="P6" t="n">
-        <v>748144.0415613037</v>
+        <v>752809.0701179379</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27436,10 +27436,10 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27448,7 +27448,7 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>307.3903671255648</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>56.51176829727007</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27499,7 +27499,7 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>98.42839661193702</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>32.07828453980449</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>338.8853128461341</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
+        <v>255.4212779793597</v>
+      </c>
+      <c r="V4" t="n">
         <v>400</v>
       </c>
-      <c r="V4" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27670,10 +27670,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>307.3903671255648</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27721,13 +27721,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>400</v>
       </c>
-      <c r="T5" t="n">
-        <v>307.3903671255644</v>
-      </c>
       <c r="U5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27752,19 +27752,19 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>158.6236956112199</v>
       </c>
       <c r="E6" t="n">
-        <v>193.9840721817118</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>399.3318877705103</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27840,10 +27840,10 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T7" t="n">
         <v>400</v>
-      </c>
-      <c r="T7" t="n">
-        <v>295.8364148149706</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
@@ -27891,10 +27891,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27916,16 +27916,16 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>307.3903671255647</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27955,22 +27955,22 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>56.51176829727058</v>
       </c>
       <c r="X8" t="n">
         <v>400</v>
@@ -27992,10 +27992,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>159.4007615079257</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,13 +28034,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>232.2755525023269</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
@@ -28074,22 +28074,22 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>386.5333200380958</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>291.4584979623525</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>19.1168712588389</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883863</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28490,16 +28490,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>166.1982915220774</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>251</v>
-      </c>
-      <c r="O15" t="n">
-        <v>166.1982915220776</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28718,31 +28718,31 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>44.46493928527482</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>279</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
         <v>279</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>155.6705902671031</v>
-      </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28955,25 +28955,25 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>217.5442043757544</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
-      </c>
-      <c r="J21" t="n">
-        <v>279</v>
-      </c>
-      <c r="K21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283643</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29152,7 +29152,7 @@
         <v>279</v>
       </c>
       <c r="V23" t="n">
-        <v>279.0000000000078</v>
+        <v>279</v>
       </c>
       <c r="W23" t="n">
         <v>279</v>
@@ -29192,31 +29192,31 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>279</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>279</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29441,7 +29441,7 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29669,7 +29669,7 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883917</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29684,7 +29684,7 @@
         <v>225</v>
       </c>
       <c r="O30" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P30" t="n">
         <v>225</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>291</v>
+        <v>282.5434086145851</v>
       </c>
       <c r="T32" t="n">
         <v>291</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -29903,25 +29903,25 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>291</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>227.0158611578289</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>9.889475266480417</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -30046,7 +30046,7 @@
         <v>291</v>
       </c>
       <c r="D35" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
       <c r="E35" t="n">
         <v>291</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="36">
@@ -30140,31 +30140,31 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>291</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>127.8102101760009</v>
       </c>
       <c r="O36" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>291</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30280,7 +30280,7 @@
         <v>291</v>
       </c>
       <c r="C38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="D38" t="n">
         <v>291</v>
@@ -30346,7 +30346,7 @@
         <v>291</v>
       </c>
       <c r="Y38" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="39">
@@ -30380,16 +30380,16 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>127.8102101760009</v>
       </c>
       <c r="K39" t="n">
-        <v>9.889475266480332</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="M39" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>291</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>291</v>
@@ -30617,7 +30617,7 @@
         <v>213</v>
       </c>
       <c r="J42" t="n">
-        <v>213</v>
+        <v>9.611785124016606</v>
       </c>
       <c r="K42" t="n">
         <v>213</v>
@@ -30629,7 +30629,7 @@
         <v>213</v>
       </c>
       <c r="N42" t="n">
-        <v>158.5978143635411</v>
+        <v>213</v>
       </c>
       <c r="O42" t="n">
         <v>213</v>
@@ -30693,10 +30693,10 @@
         <v>213</v>
       </c>
       <c r="I43" t="n">
-        <v>206.3691315106685</v>
+        <v>213</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>213</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,13 +30726,13 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>210.0245665062577</v>
+        <v>213</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>213</v>
       </c>
       <c r="V43" t="n">
-        <v>199.1703102162162</v>
+        <v>213</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30857,7 +30857,7 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>187</v>
+        <v>161.0457473881675</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30866,10 +30866,10 @@
         <v>187</v>
       </c>
       <c r="N45" t="n">
-        <v>41.74979257442701</v>
+        <v>187</v>
       </c>
       <c r="O45" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>187</v>
       </c>
       <c r="J46" t="n">
-        <v>103.4311288964837</v>
+        <v>187</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>150.9583912744579</v>
+        <v>187</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34746,7 +34746,7 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34901,10 +34901,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>303.6163640102263</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34934,19 +34934,19 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>104.4628867049018</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>112.2180874334316</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35126,10 +35126,10 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>85.81184830871291</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35177,10 +35177,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35238,7 +35238,7 @@
         <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -35360,22 +35360,22 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>157.7621939364772</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>256.1895491264447</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35411,16 +35411,16 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,10 +35469,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>435.3966095009883</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>293.2082466075259</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734918</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,25 +35691,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>435.2066046459229</v>
+      </c>
+      <c r="P14" t="n">
         <v>814</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35776,16 +35776,16 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>440.2896668707643</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>407.6553134248239</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
@@ -35931,16 +35931,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>64.42599844307665</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>337.9359563968417</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>814</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,31 +36004,31 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>235.5687939260661</v>
       </c>
       <c r="L18" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>397.1276121698494</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>435.2066046459229</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="R20" t="n">
         <v>5.512089101654111e-11</v>
@@ -36241,16 +36241,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>274.091375348687</v>
+        <v>491.6355797244414</v>
       </c>
       <c r="M21" t="n">
         <v>86.95004216450428</v>
@@ -36259,7 +36259,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
         <v>113.6660045146532</v>
@@ -36405,7 +36405,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -36417,16 +36417,16 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
+        <v>435.3966095009883</v>
+      </c>
+      <c r="P23" t="n">
         <v>814</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.981979528761874e-11</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>125.2086062376757</v>
@@ -36487,22 +36487,22 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>242.6206324316074</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>392.6660045146532</v>
+        <v>158.1309437999284</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>603.4970285185401</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36657,10 +36657,10 @@
         <v>773.0000000000275</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000275</v>
       </c>
       <c r="Q26" t="n">
-        <v>281.8836413365349</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36727,7 +36727,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36882,7 +36882,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>314.0531751575193</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,10 +36891,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>314.0531751575191</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="P29" t="n">
-        <v>773.0000000000348</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,7 +36955,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36970,7 +36970,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P30" t="n">
         <v>338.6660045146532</v>
@@ -37116,7 +37116,7 @@
         <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320761396</v>
+        <v>727.1079320760389</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
@@ -37189,25 +37189,25 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>191.1038546407913</v>
+        <v>482.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>313.9659033223331</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>241.4570219027464</v>
+        <v>251.3464971692268</v>
       </c>
       <c r="P33" t="n">
         <v>113.6660045146532</v>
@@ -37353,10 +37353,10 @@
         <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760183</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320760291</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000493</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37438,19 +37438,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
-        <v>86.95004216450428</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>134.6265501086548</v>
+        <v>262.4367602846557</v>
       </c>
       <c r="O36" t="n">
-        <v>468.4728830605751</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>117.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37590,10 +37590,10 @@
         <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
+        <v>727.1079320760786</v>
+      </c>
+      <c r="L38" t="n">
         <v>773</v>
-      </c>
-      <c r="L38" t="n">
-        <v>727.107932076007</v>
       </c>
       <c r="M38" t="n">
         <v>773.0000000000566</v>
@@ -37666,16 +37666,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>125.2086062376757</v>
+        <v>253.0188164136766</v>
       </c>
       <c r="K39" t="n">
-        <v>200.9933299072716</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>274.091375348687</v>
+        <v>565.0913753486871</v>
       </c>
       <c r="M39" t="n">
-        <v>377.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37687,7 +37687,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>117.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37830,19 +37830,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>773</v>
+        <v>216.5925220533434</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>113.18697554247</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.0000000000639</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>338.2086062376757</v>
+        <v>134.8203913616923</v>
       </c>
       <c r="K42" t="n">
         <v>404.1038546407913</v>
@@ -37915,7 +37915,7 @@
         <v>299.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>293.2243644721959</v>
+        <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
         <v>454.4570219027464</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>29.73567589055027</v>
+        <v>36.36654437988173</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>177.7310511640922</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.975433493742287</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>62.04160872554206</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>13.82968978378381</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>314.0531751574757</v>
+        <v>773</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>773.0000000000784</v>
+        <v>732.6014399614226</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38143,7 +38143,7 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>378.1038546407913</v>
+        <v>352.1496020289588</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38152,10 +38152,10 @@
         <v>273.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>176.3763426830818</v>
+        <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>428.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P45" t="n">
         <v>300.6660045146532</v>
@@ -38219,7 +38219,7 @@
         <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
-        <v>68.16218006057591</v>
+        <v>151.7310511640922</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>36.04160872554206</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
